--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486733_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486733_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. MARTIN LLUNA</t>
+          <t>A. TORRES MUNICIO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8842</v>
+        <v>1.4093</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1787</v>
+        <v>0.6063</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7055</v>
+        <v>0.803</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8355</v>
+        <v>-2.1422</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.2062</v>
+        <v>-0.0692</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3707</v>
+        <v>-2.073</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8759</v>
+        <v>-1.3479</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7945</v>
+        <v>0.759</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0814</v>
+        <v>-2.1068</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.7113</v>
+        <v>-0.7943</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.0007</v>
+        <v>-0.8282</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2893</v>
+        <v>0.0338</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3169</v>
+        <v>1.3515</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3169</v>
+        <v>1.5446</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4027</v>
+        <v>0.3584</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3028</v>
+        <v>0.6339</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0999</v>
+        <v>-0.2755</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.8415</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. VALVERDE SASTRE</t>
+          <t>D. MARTIN LLUNA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5805</v>
+        <v>0.9987</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4198</v>
+        <v>0.765</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0002</v>
+        <v>0.2337</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3574</v>
+        <v>-0.8355</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5717</v>
+        <v>-1.2062</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9291</v>
+        <v>0.3707</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.076</v>
+        <v>0.8759</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1573</v>
+        <v>0.7945</v>
       </c>
       <c r="L3" t="n">
         <v>0.0814</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4334</v>
+        <v>-1.7113</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4143</v>
+        <v>-2.0007</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8477</v>
+        <v>0.2893</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1931</v>
+        <v>2.3169</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3515</v>
+        <v>2.3169</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2577</v>
+        <v>-0.4828</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1855</v>
+        <v>-0.1108</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0722</v>
+        <v>-0.3719</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3709</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2855</v>
+        <v>0.7544</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0236</v>
+        <v>0.4924</v>
       </c>
       <c r="F4" t="n">
         <v>0.2619</v>
@@ -766,10 +766,10 @@
         <v>0.1931</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1104</v>
+        <v>0.3585</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1104</v>
+        <v>0.3585</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. TORRES MUNICIO</t>
+          <t>D. AVILA MERCADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1681</v>
+        <v>0.6636</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3866</v>
+        <v>-0.0592</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5547</v>
+        <v>0.7228</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.1422</v>
+        <v>-0.5876</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0692</v>
+        <v>-0.8068</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.073</v>
+        <v>0.2193</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.3479</v>
+        <v>0.9106</v>
       </c>
       <c r="K5" t="n">
-        <v>0.759</v>
+        <v>1.6768</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.1068</v>
+        <v>-0.7663</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7943</v>
+        <v>-1.4981</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8282</v>
+        <v>-2.4837</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0338</v>
+        <v>0.9856</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3515</v>
+        <v>0.7723</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1931</v>
+        <v>-1.9308</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5446</v>
+        <v>2.7031</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8828</v>
+        <v>-1.0345</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.359</v>
+        <v>-0.5523</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5238</v>
+        <v>-0.4822</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8415</v>
+        <v>1.5133</v>
       </c>
       <c r="W5" t="n">
         <v>1.5133</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. AVILA MERCADO</t>
+          <t>J. VALVERDE SASTRE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.1296</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5281</v>
+        <v>-0.7713</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5986</v>
+        <v>0.9009</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5876</v>
+        <v>0.3574</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8068</v>
+        <v>-0.5717</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2193</v>
+        <v>0.9291</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9106</v>
+        <v>-0.076</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6768</v>
+        <v>-0.1573</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7663</v>
+        <v>0.0814</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4981</v>
+        <v>0.4334</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.4837</v>
+        <v>-0.4143</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9856</v>
+        <v>0.8477</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7723</v>
+        <v>0.1931</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9308</v>
+        <v>-1.1585</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7031</v>
+        <v>1.3515</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6275</v>
+        <v>0.8068</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0212</v>
+        <v>0.834</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.0272</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5133</v>
+        <v>-1.2277</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5133</v>
+        <v>-0.3709</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.8568</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SOLE MOURATAY</t>
+          <t>J. ONGIL FERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0163</v>
+        <v>-1.0739</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7672</v>
+        <v>-0.1533</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7835</v>
+        <v>-0.9206</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.6296</v>
+        <v>-0.9397</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.6131</v>
+        <v>-0.4898</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0165</v>
+        <v>-0.4499</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.6216</v>
+        <v>0.1435</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.7159</v>
+        <v>0.0621</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.9057</v>
+        <v>0.0814</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.0081</v>
+        <v>-1.0832</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.8972</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1108</v>
+        <v>-0.5313</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7377</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9654</v>
+        <v>-1.1585</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7031</v>
+        <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>1.092</v>
+        <v>0.9584</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7716</v>
+        <v>0.8617</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3204</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>2.7836</v>
+        <v>-0.8995</v>
       </c>
       <c r="W7" t="n">
-        <v>4.5825</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7989</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ONGIL FERNANDEZ</t>
+          <t>J. BECERRA ORDOÑEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4697</v>
+        <v>-1.1899</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5739</v>
+        <v>0.7627</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8958</v>
+        <v>-1.9527</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9397</v>
+        <v>-0.4238</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4898</v>
+        <v>-2.0899</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4499</v>
+        <v>1.6661</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1435</v>
+        <v>0.8803</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0621</v>
+        <v>-0.5032</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0814</v>
+        <v>1.3835</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0832</v>
+        <v>-1.3041</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-1.5867</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5313</v>
+        <v>0.2826</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1931</v>
+        <v>1.9308</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9654</v>
+        <v>1.9308</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5626</v>
+        <v>-0.2415</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4411</v>
+        <v>-0.1175</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1215</v>
+        <v>-0.124</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8995</v>
+        <v>-2.4554</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8995</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. BECERRA ORDOÑEZ</t>
+          <t>M. SOLE MOURATAY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8809</v>
+        <v>-2.0879</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2456</v>
+        <v>0.0432</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1265</v>
+        <v>-2.1311</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4238</v>
+        <v>-6.6296</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0899</v>
+        <v>-4.6131</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6661</v>
+        <v>-2.0165</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8803</v>
+        <v>-3.6216</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5032</v>
+        <v>-1.7159</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3835</v>
+        <v>-1.9057</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3041</v>
+        <v>-3.0081</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5867</v>
+        <v>-2.8972</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2826</v>
+        <v>-0.1108</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9308</v>
+        <v>1.7377</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9308</v>
+        <v>2.7031</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9325</v>
+        <v>0.0204</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6347</v>
+        <v>0.0476</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2978</v>
+        <v>-0.0272</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4554</v>
+        <v>2.7836</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>4.5825</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4554</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MARTÍNEZ LAGO</t>
+          <t>J. JIMENEZ LAHOZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3779</v>
+        <v>-2.239</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8018</v>
+        <v>-2.2834</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5761</v>
+        <v>0.0444</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.2267</v>
+        <v>-2.0112</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.7301</v>
+        <v>-3.5169</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4966</v>
+        <v>1.5057</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.8672</v>
+        <v>-1.0516</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4883</v>
+        <v>-1.9989</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.379</v>
+        <v>0.9474</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3594</v>
+        <v>-0.9596</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2418</v>
+        <v>-1.5179</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1176</v>
+        <v>0.5583</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.1585</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1585</v>
+        <v>-0.9654</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1585</v>
+        <v>2.1239</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4473</v>
+        <v>-0.7724</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3091</v>
+        <v>-0.5521</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1381</v>
+        <v>-0.2204</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5985</v>
+        <v>-0.6138</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0852</v>
+        <v>0.2856</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5133</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LAHOZ</t>
+          <t>A. MARTÍNEZ LAGO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9065</v>
+        <v>-4.2808</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7523</v>
+        <v>-2.7047</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1542</v>
+        <v>-1.5761</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0112</v>
+        <v>-4.2267</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.5169</v>
+        <v>-2.7301</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5057</v>
+        <v>-1.4966</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0516</v>
+        <v>-2.8672</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9989</v>
+        <v>-1.4883</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9474</v>
+        <v>-1.379</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9596</v>
+        <v>-1.3594</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5179</v>
+        <v>-1.2418</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5583</v>
+        <v>-0.1176</v>
       </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-1.1585</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.1585</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-0.9654</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.1239</v>
-      </c>
       <c r="S11" t="n">
-        <v>-1.44</v>
+        <v>1.5444</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0209</v>
+        <v>1.4063</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.419</v>
+        <v>0.1381</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6138</v>
+        <v>-1.5985</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2856</v>
+        <v>-0.0852</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8995</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.9255</v>
+        <v>-6.8443</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8445</v>
+        <v>-4.9619</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.081</v>
+        <v>-1.8824</v>
       </c>
       <c r="G12" t="n">
         <v>-3.6349</v>
@@ -1390,13 +1390,13 @@
         <v>1.3515</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.495</v>
+        <v>-0.4138</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9381</v>
+        <v>-0.0555</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5569</v>
+        <v>-0.3583</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2856</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.588</v>
+        <v>-13.7602</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.091899999999999</v>
+        <v>-8.264199999999999</v>
       </c>
       <c r="F13" t="n">
         <v>-5.4962</v>
@@ -1447,7 +1447,7 @@
         <v>-3.0951</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.961699999999999</v>
+        <v>-4.9617</v>
       </c>
       <c r="M13" t="n">
         <v>-12.9064</v>
@@ -1468,16 +1468,16 @@
         <v>18.3424</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2740999999999998</v>
+        <v>1.1019</v>
       </c>
       <c r="T13" t="n">
-        <v>1.925799999999999</v>
+        <v>2.7538</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.6518</v>
+        <v>-1.652</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6564999999999999</v>
+        <v>-0.6565000000000003</v>
       </c>
       <c r="W13" t="n">
         <v>8.623699999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3623</v>
+        <v>5.2533</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5647</v>
+        <v>3.1511</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7976</v>
+        <v>2.1023</v>
       </c>
       <c r="G14" t="n">
         <v>7.7949</v>
@@ -1546,13 +1546,13 @@
         <v>0.9654</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4057</v>
+        <v>1.2967</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9374</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4683</v>
+        <v>0.773</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9421</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9373</v>
+        <v>5.1952</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1645</v>
+        <v>5.0611</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2273</v>
+        <v>0.1341</v>
       </c>
       <c r="G15" t="n">
         <v>4.8504</v>
@@ -1624,13 +1624,13 @@
         <v>0.5792</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1215</v>
+        <v>0.3794</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3859</v>
+        <v>0.2825</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2645</v>
+        <v>0.0969</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6138</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4776</v>
+        <v>3.4212</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7723</v>
+        <v>2.2552</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7053</v>
+        <v>1.166</v>
       </c>
       <c r="G16" t="n">
         <v>3.1138</v>
@@ -1702,13 +1702,13 @@
         <v>0.5792</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6276</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.31</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1432</v>
+        <v>0.3175</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8995</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3984</v>
+        <v>2.7598</v>
       </c>
       <c r="E17" t="n">
         <v>1.4016</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9968</v>
+        <v>1.3582</v>
       </c>
       <c r="G17" t="n">
         <v>2.3499</v>
@@ -1780,13 +1780,13 @@
         <v>0.5792</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8164</v>
+        <v>-0.455</v>
       </c>
       <c r="T17" t="n">
         <v>-0.3311</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4853</v>
+        <v>-0.1239</v>
       </c>
       <c r="V17" t="n">
         <v>0.2856</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. VIDARTE CANO</t>
+          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3581</v>
+        <v>2.3552</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0877</v>
+        <v>2.201</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2704</v>
+        <v>0.1542</v>
       </c>
       <c r="G18" t="n">
-        <v>4.6</v>
+        <v>0.8008</v>
       </c>
       <c r="H18" t="n">
-        <v>1.496</v>
+        <v>1.1444</v>
       </c>
       <c r="I18" t="n">
-        <v>3.1039</v>
+        <v>-0.3435</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8155</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.456</v>
       </c>
       <c r="L18" t="n">
-        <v>2.939</v>
+        <v>-1.4535</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7845</v>
+        <v>1.7983</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6884</v>
       </c>
       <c r="O18" t="n">
-        <v>0.165</v>
+        <v>1.1099</v>
       </c>
       <c r="P18" t="n">
-        <v>-5.02</v>
+        <v>1.7377</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.7923</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7723</v>
+        <v>1.7377</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5505</v>
+        <v>0.1449</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9374</v>
+        <v>0.1719</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6131</v>
+        <v>-0.027</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2277</v>
+        <v>-0.3282</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1271</v>
+        <v>3.0266</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8995</v>
+        <v>-3.3548</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
+          <t>B. VIDARTE CANO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7966</v>
+        <v>1.8629</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8908</v>
+        <v>0.7774</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0941</v>
+        <v>1.0855</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8008</v>
+        <v>4.6</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1444</v>
+        <v>1.496</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3435</v>
+        <v>3.1039</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9975000000000001</v>
+        <v>3.8155</v>
       </c>
       <c r="K19" t="n">
-        <v>0.456</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.4535</v>
+        <v>2.939</v>
       </c>
       <c r="M19" t="n">
-        <v>1.7983</v>
+        <v>0.7845</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6884</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>1.1099</v>
+        <v>0.165</v>
       </c>
       <c r="P19" t="n">
-        <v>1.7377</v>
+        <v>-5.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-5.7923</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7377</v>
+        <v>0.7723</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4137</v>
+        <v>1.0553</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1384</v>
+        <v>0.6271</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2753</v>
+        <v>0.4282</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3282</v>
+        <v>1.2277</v>
       </c>
       <c r="W19" t="n">
-        <v>3.0266</v>
+        <v>2.1271</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.3548</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0468</v>
+        <v>0.1999</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5034999999999999</v>
+        <v>0.6069</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4567</v>
+        <v>-0.407</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1313</v>
@@ -2014,13 +2014,13 @@
         <v>0.1931</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6288</v>
+        <v>-0.4758</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1104</v>
+        <v>-0.0069</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5185</v>
+        <v>-0.4688</v>
       </c>
       <c r="V20" t="n">
         <v>0.6138</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GOMEZ FRAILE</t>
+          <t>E. BUENO KNUTSEN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2002</v>
+        <v>-0.1331</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8067</v>
+        <v>-0.9051</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6066</v>
+        <v>0.772</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.276</v>
+        <v>-0.3745</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9654</v>
+        <v>0.0618</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6895</v>
+        <v>-0.4363</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2755</v>
+        <v>-0.6635</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2755</v>
+        <v>0.0621</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.7256</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0005</v>
+        <v>0.289</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6899</v>
+        <v>-0.0003</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6895</v>
+        <v>0.2893</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4966</v>
+        <v>-1.1101</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4688</v>
+        <v>-0.2416</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0278</v>
+        <v>-0.8686</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. BUENO KNUTSEN</t>
+          <t>A. GOMEZ FRAILE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5675</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2153</v>
+        <v>-1.117</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6478</v>
+        <v>0.4824</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3745</v>
+        <v>-1.276</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0618</v>
+        <v>-1.9654</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4363</v>
+        <v>0.6895</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6635</v>
+        <v>-1.2755</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0621</v>
+        <v>-1.2755</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7256</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.289</v>
+        <v>-0.0005</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0003</v>
+        <v>-0.6899</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2893</v>
+        <v>0.6895</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3515</v>
+        <v>0.5792</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3515</v>
+        <v>0.5792</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5446</v>
+        <v>0.0622</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5518</v>
+        <v>0.1585</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9927</v>
+        <v>-0.0963</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4143</v>
+        <v>-0.6573</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3138</v>
+        <v>-3.383</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8995</v>
+        <v>2.7257</v>
       </c>
       <c r="G23" t="n">
         <v>1.7072</v>
@@ -2248,13 +2248,13 @@
         <v>2.1239</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-0.186</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8554</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0876</v>
+        <v>-0.2615</v>
       </c>
       <c r="V23" t="n">
         <v>2.4554</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.2218</v>
+        <v>-1.4852</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3655</v>
+        <v>-2.9518</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1437</v>
+        <v>1.4665</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8976</v>
@@ -2326,13 +2326,13 @@
         <v>1.5446</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2742</v>
+        <v>-0.5377</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2208</v>
+        <v>0.1928</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0534</v>
+        <v>-0.7306</v>
       </c>
       <c r="V24" t="n">
         <v>0.3709</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.3853</v>
+        <v>-2.8597</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.1875</v>
+        <v>-1.6012</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1977</v>
+        <v>-1.2585</v>
       </c>
       <c r="G25" t="n">
         <v>-0.5742</v>
@@ -2404,13 +2404,13 @@
         <v>0.5792</v>
       </c>
       <c r="S25" t="n">
-        <v>0.08840000000000001</v>
+        <v>-0.386</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3032</v>
+        <v>-0.1105</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2148</v>
+        <v>-0.2756</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5133</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>14.588</v>
+        <v>15.2776</v>
       </c>
       <c r="E26" t="n">
-        <v>5.496299999999999</v>
+        <v>5.496199999999998</v>
       </c>
       <c r="F26" t="n">
-        <v>9.091900000000001</v>
+        <v>9.7814</v>
       </c>
       <c r="G26" t="n">
         <v>20.9634</v>
@@ -2464,10 +2464,10 @@
         <v>-2.2713</v>
       </c>
       <c r="M26" t="n">
-        <v>8.056899999999999</v>
+        <v>8.056900000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>3.0952</v>
+        <v>3.095200000000001</v>
       </c>
       <c r="O26" t="n">
         <v>4.9617</v>
@@ -2482,13 +2482,13 @@
         <v>11.5845</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2739999999999999</v>
+        <v>0.4155</v>
       </c>
       <c r="T26" t="n">
-        <v>1.6519</v>
+        <v>1.6518</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.9261</v>
+        <v>-1.2367</v>
       </c>
       <c r="V26" t="n">
         <v>0.6565000000000003</v>
